--- a/backtest_runs/20260410_193731/by_symbol/SCBPL/SCBPL.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/SCBPL/SCBPL.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -541,7 +541,7 @@
         <v>-5014.01999999999</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>94985.98000000001</v>
@@ -679,7 +679,7 @@
         <v>-5795.020000000001</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>91986.94</v>
@@ -909,7 +909,7 @@
         <v>-2608.540000000003</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>98719.15999999999</v>
@@ -955,7 +955,7 @@
         <v>-4842.199999999991</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K11" s="2" t="n">
         <v>93876.95999999999</v>
@@ -1047,7 +1047,7 @@
         <v>-874.7200000000036</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>93095.95999999999</v>
@@ -1139,7 +1139,7 @@
         <v>-656.0400000000027</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K15" s="2" t="n">
         <v>93361.5</v>
@@ -1185,7 +1185,7 @@
         <v>-1811.920000000006</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>91549.57999999999</v>
@@ -1231,7 +1231,7 @@
         <v>-1593.239999999994</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>89956.34</v>
@@ -1277,7 +1277,7 @@
         <v>-6107.420000000006</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>83848.92</v>
@@ -1323,7 +1323,7 @@
         <v>-7372.639999999999</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>76476.28</v>
@@ -1415,7 +1415,7 @@
         <v>-781</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>77975.79999999999</v>
@@ -1461,7 +1461,7 @@
         <v>-452.9799999999987</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>77522.81999999999</v>
